--- a/data/samples/samples/15-9-F-14_D03_2026-03-03.xlsx
+++ b/data/samples/samples/15-9-F-14_D03_2026-03-03.xlsx
@@ -1083,14 +1083,14 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>08:00 08:30 接单根，耗时 18 分钟。</t>
+          <t>08:30 08:30 接单根，耗时 18 分钟。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>11:00 11:15 循环调整泥浆性能，密度提至 1.23 g/cm3，漏斗粘度 44 s。</t>
+          <t>11:15 11:15 循环调整泥浆性能，密度提至 1.23 g/cm3，漏斗粘度 44 s。</t>
         </is>
       </c>
     </row>
@@ -1104,21 +1104,21 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>16:00 16:45 安全检查：井控装备完好，防喷器控制系统压力正常。</t>
+          <t>16:45 16:45 安全检查：井控装备完好，防喷器控制系统压力正常。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>18:00 18:45 接单根，耗时 18 分钟。</t>
+          <t>18:45 18:45 接单根，耗时 18 分钟。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>20:00 20:30 短起下检查井眼，返砂正常。</t>
+          <t>20:30 20:30 短起下检查井眼，返砂正常。</t>
         </is>
       </c>
     </row>
